--- a/sample_files/sales_data.xlsx
+++ b/sample_files/sales_data.xlsx
@@ -481,20 +481,20 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2023-02-15</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>452</v>
+        <v>401</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -504,16 +504,16 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tennis Racket</t>
+          <t>Makeup Kit</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>$1369.99</t>
+          <t>$358.76</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3">
@@ -522,37 +522,37 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>08/06/2022</t>
+          <t>07/21/2023</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>224</v>
+        <v>343</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>1637.906203106449</v>
+        <v>686.2094787515999</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4">
@@ -561,11 +561,11 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>10/28/2022</t>
+          <t>05-Nov-2022</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -574,24 +574,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Shoes</t>
+          <t>T-shirt</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>1676.446101639573</v>
+        <v>1805.319415080301</v>
       </c>
       <c r="I4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -600,33 +600,37 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2023-05-15</t>
+          <t>19-Jan-2022</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Books</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>81.74407208476573</v>
+        <v>1088.53665155253</v>
       </c>
       <c r="I5" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6">
@@ -635,27 +639,37 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11-Sep-2022</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>2022-12-21</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>106</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Books</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Bank Transfer</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pending</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Textbook</t>
+          <t>T-shirt</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>334.6244076233867</v>
+        <v>1211.00969558681</v>
       </c>
       <c r="I6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7">
@@ -664,35 +678,35 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2022-09-23</t>
+          <t>14-Mar-2023</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>106</v>
+        <v>143</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Microwave</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>398.55 USD</t>
+          <t>1143.66 USD</t>
         </is>
       </c>
       <c r="I7" t="n">
@@ -705,37 +719,37 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22-Jun-2022</t>
+          <t>2023-11-06</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>254</v>
+        <v>34</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Coffee Maker</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>782.8586782953062</v>
+        <v>1127.886652456084</v>
       </c>
       <c r="I8" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -744,39 +758,39 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>23-Sep-2023</t>
+          <t>06-Sep-2022</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Children's</t>
+          <t>Headphones</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>€251,53</t>
+          <t>€1250,70</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -785,15 +799,15 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>07/22/2023</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>428</v>
+        <v>404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -803,19 +817,19 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Makeup Kit</t>
+          <t>Dress</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1532.987160399884</v>
+        <v>625.2756123826626</v>
       </c>
       <c r="I10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="11">
@@ -824,37 +838,37 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>30-Mar-2022</t>
+          <t>2023-02-12</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Vacuum Cleaner</t>
+          <t>Tennis Racket</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>616.3004146869371</v>
+        <v>590.3968508944996</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
@@ -863,35 +877,39 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>05/20/2023</t>
+          <t>2022-04-24</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>363</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>207</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dumbbells</t>
+          <t>Dress</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>$174.10</t>
+          <t>$1036.87</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -900,37 +918,37 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2023-07-22</t>
+          <t>10/11/2022</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>426</v>
+        <v>77</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Toaster</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>1634.268078718228</v>
+        <v>1523.853327664455</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -939,31 +957,37 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2022-08-26</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>01-Apr-2022</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>273</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Headphones</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1364.505050322409</v>
+        <v>1117.146845185243</v>
       </c>
       <c r="I14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="15">
@@ -972,15 +996,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>05/02/2022</t>
+          <t>21-Aug-2022</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>382</v>
+        <v>477</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -990,19 +1014,19 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dress</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>756.7395065975389</v>
+        <v>1417.82082819727</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
@@ -1011,35 +1035,35 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2023-04-04</t>
+          <t>2022-06-16</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>382</v>
+        <v>245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Microwave</t>
+          <t>Non-fiction</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>€1166,57</t>
+          <t>€1991,72</t>
         </is>
       </c>
       <c r="I16" t="n">
@@ -1052,38 +1076,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>16-Jun-2023</t>
+          <t>2023-05-31</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>26</v>
+        <v>444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tennis Racket</t>
+          <t>Children's</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>302.57 USD</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>1035.73 USD</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1091,37 +1117,33 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2022-10-17</t>
+          <t>2023-08-06</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Bank Transfer</t>
-        </is>
-      </c>
+          <t>Home &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Vacuum Cleaner</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>57.41968640734194</v>
+        <v>1972.631157489343</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="19">
@@ -1130,37 +1152,37 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2023-01-26</t>
+          <t>08/06/2023</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>21</v>
+        <v>471</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Running Shoes</t>
+          <t>Perfume</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>377.8238207742136</v>
+        <v>602.0030874532021</v>
       </c>
       <c r="I19" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -1169,20 +1191,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12/09/2022</t>
+          <t>10-Mar-2023</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>392</v>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Beauty</t>
-        </is>
-      </c>
+        <v>484</v>
+      </c>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1192,14 +1210,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Perfume</t>
+          <t>Dumbbells</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>1377.887724622244</v>
+        <v>163.8923643429136</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
@@ -1208,15 +1226,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2022-10-29</t>
+          <t>06/11/2022</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>377</v>
+        <v>220</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1226,19 +1244,19 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>T-shirt</t>
+          <t>Non-fiction</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>715.7622589965322</v>
+        <v>1971.104619978202</v>
       </c>
       <c r="I21" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
@@ -1247,40 +1265,38 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>09/14/2023</t>
+          <t>2022-03-25</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Non-fiction</t>
+          <t>Perfume</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>$717.97</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>5</v>
-      </c>
+          <t>$273.59</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1288,35 +1304,39 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>05/12/2022</t>
+          <t>07/08/2022</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>431</v>
+        <v>209</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Books</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Non-fiction</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>€188,52</t>
+          <t>€208,80</t>
         </is>
       </c>
       <c r="I23" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
@@ -1325,37 +1345,35 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>01/03/2023</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>55</v>
-      </c>
+          <t>01/31/2023</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Blender</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>814.5522924940374</v>
+        <v>582.7666310381737</v>
       </c>
       <c r="I24" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1364,20 +1382,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>11/15/2022</t>
+          <t>05/08/2022</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>268</v>
+        <v>235</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1387,14 +1405,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Textbook</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1795.302100918475</v>
+        <v>711.6876468678125</v>
       </c>
       <c r="I25" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26">
@@ -1403,15 +1421,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>20-Jun-2022</t>
+          <t>2023-10-10</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>460</v>
+        <v>7</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1421,19 +1439,19 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Moisturizer</t>
+          <t>Dumbbells</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>761.6661103990593</v>
+        <v>1037.747819794027</v>
       </c>
       <c r="I26" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27">
@@ -1442,11 +1460,11 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>20-May-2023</t>
+          <t>2022-09-23</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>496</v>
+        <v>449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1455,26 +1473,26 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tennis Racket</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1990.39 USD</t>
+          <t>582.66 USD</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="28">
@@ -1483,36 +1501,38 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>08/25/2023</t>
+          <t>11/10/2023</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>217</v>
+        <v>160</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>124.6041045889691</v>
-      </c>
-      <c r="I28" t="inlineStr"/>
+        <v>1747.525878062125</v>
+      </c>
+      <c r="I28" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1520,34 +1540,34 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>18-Apr-2022</t>
+          <t>2022-12-01</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>198</v>
+        <v>442</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Toaster</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>741.8170343505925</v>
+        <v>1067.928035327647</v>
       </c>
       <c r="I29" t="n">
         <v>10</v>
@@ -1559,35 +1579,33 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>01/10/2023</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>174</v>
-      </c>
+          <t>04/07/2023</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Tennis Racket</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>€781,20</t>
+          <t>€456,33</t>
         </is>
       </c>
       <c r="I30" t="n">
@@ -1600,20 +1618,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2023-05-16</t>
+          <t>11/27/2023</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>29</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Beauty</t>
-        </is>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1623,11 +1637,11 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hairdryer</t>
+          <t>Makeup Kit</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>102.4935325882937</v>
+        <v>987.3003466015963</v>
       </c>
       <c r="I31" t="n">
         <v>8</v>
@@ -1639,35 +1653,39 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>19-Jul-2022</t>
+          <t>01/16/2023</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>332</v>
+        <v>358</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hairdryer</t>
+          <t>Dumbbells</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>$1971.22</t>
+          <t>$1668.39</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -1676,37 +1694,37 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>01-Nov-2023</t>
+          <t>04/25/2022</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>459</v>
+        <v>382</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>1571.162878636116</v>
+        <v>1839.942624460894</v>
       </c>
       <c r="I33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34">
@@ -1715,33 +1733,37 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>09/26/2023</t>
+          <t>05/04/2023</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>311</v>
+        <v>462</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Non-fiction</t>
+        </is>
+      </c>
       <c r="H34" t="n">
-        <v>833.9463859018077</v>
+        <v>1673.330438618467</v>
       </c>
       <c r="I34" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -1750,11 +1772,11 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>18-May-2023</t>
+          <t>10/26/2023</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1763,24 +1785,24 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>1215.213010137483</v>
+        <v>1097.400647305886</v>
       </c>
       <c r="I35" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -1789,20 +1811,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2022-04-14</t>
+          <t>2023-02-04</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>428</v>
+        <v>225</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1812,14 +1834,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>T-shirt</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>643.3087966146596</v>
+        <v>897.4337363416221</v>
       </c>
       <c r="I36" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37">
@@ -1828,39 +1850,39 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>07-Jan-2023</t>
+          <t>10/26/2023</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>334</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Shampoo</t>
+          <t>Textbook</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>€896,96</t>
+          <t>€385,88</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38">
@@ -1869,33 +1891,37 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18-Dec-2022</t>
+          <t>04-Dec-2023</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>116</v>
+        <v>494</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Children's</t>
+        </is>
+      </c>
       <c r="H38" t="n">
-        <v>1847.967322749842</v>
+        <v>1606.575114676577</v>
       </c>
       <c r="I38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39">
@@ -1904,20 +1930,16 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>07-Jun-2022</t>
+          <t>08/20/2022</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>183</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1927,14 +1949,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Coffee Maker</t>
+          <t>Headphones</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>348.6382882720691</v>
+        <v>119.2513283728423</v>
       </c>
       <c r="I39" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="40">
@@ -1943,37 +1965,37 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>19-Jan-2022</t>
+          <t>2022-03-11</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>472</v>
+        <v>177</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Blender</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1255.229176783303</v>
+        <v>1668.161091179227</v>
       </c>
       <c r="I40" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -1982,11 +2004,11 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2023-03-19</t>
+          <t>14-Apr-2022</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>27</v>
+        <v>241</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2000,16 +2022,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>625.5928143644663</v>
+        <v>1541.342794740153</v>
       </c>
       <c r="I41" t="n">
         <v>7</v>
@@ -2021,11 +2043,11 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>01-Jul-2023</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6</v>
+        <v>213</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2034,22 +2056,26 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Cash</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>CANCELLED</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>T-shirt</t>
+          <t>Jacket</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>$159.56</t>
+          <t>$51.99</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43">
@@ -2058,37 +2084,33 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2022-05-31</t>
+          <t>07/02/2022</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>333</v>
+        <v>199</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Cash</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Microwave</t>
+          <t>Toaster</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>1791.022757783797</v>
+        <v>1970.384185262752</v>
       </c>
       <c r="I43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="44">
@@ -2097,20 +2119,20 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
+          <t>2022-05-09</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>117</v>
+        <v>275</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2120,16 +2142,16 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Shoes</t>
+          <t>Microwave</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>€482,79</t>
+          <t>€1917,07</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="45">
@@ -2138,34 +2160,34 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>02/09/2022</t>
+          <t>2022-02-05</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>451</v>
+        <v>325</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Perfume</t>
+          <t>Running Shoes</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>1962.406855791115</v>
+        <v>467.2876330678129</v>
       </c>
       <c r="I45" t="n">
         <v>10</v>
@@ -2177,13 +2199,15 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2023-02-08</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>25-Jun-2023</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>495</v>
+      </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2193,20 +2217,18 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Headphones</t>
+          <t>Makeup Kit</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>68.02826368779871</v>
-      </c>
-      <c r="I46" t="n">
-        <v>5</v>
-      </c>
+        <v>1568.273226193943</v>
+      </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -2214,35 +2236,35 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2023-03-19</t>
+          <t>04/18/2023</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>437</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Beauty</t>
-        </is>
-      </c>
+        <v>338</v>
+      </c>
+      <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Yoga Mat</t>
+        </is>
+      </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>150.34 USD</t>
+          <t>674.28 USD</t>
         </is>
       </c>
       <c r="I47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="48">
@@ -2251,37 +2273,37 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>08-Dec-2022</t>
+          <t>12/08/2023</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>475</v>
+        <v>320</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Yoga Mat</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>156.87154223472</v>
+        <v>225.3271657011216</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
@@ -2290,15 +2312,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>02-Dec-2023</t>
+          <t>06-Sep-2023</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>474</v>
+        <v>385</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2308,19 +2330,19 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>200.5180673767307</v>
+        <v>60.7981691062237</v>
       </c>
       <c r="I49" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -2329,11 +2351,11 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2022-06-02</t>
+          <t>06-Nov-2023</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>337</v>
+        <v>454</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2342,24 +2364,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Makeup Kit</t>
+          <t>Shampoo</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>634.7140776087646</v>
+        <v>82.68008802587883</v>
       </c>
       <c r="I50" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="51">
@@ -2368,39 +2390,39 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>19-Jul-2022</t>
+          <t>2023-12-21</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>222</v>
+        <v>162</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Headphones</t>
+          <t>Tennis Racket</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>€1787,75</t>
+          <t>€217,91</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52">
@@ -2409,39 +2431,39 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2022-07-15</t>
+          <t>26-Mar-2022</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>59</v>
+        <v>367</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Microwave</t>
+          <t>Makeup Kit</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>$1725.43</t>
+          <t>$1936.57</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -2450,20 +2472,20 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>01/08/2023</t>
+          <t>01-Jun-2022</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>192</v>
+        <v>500</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2473,14 +2495,14 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Toaster</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1392.775117866737</v>
+        <v>1251.082694386056</v>
       </c>
       <c r="I53" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="54">
@@ -2489,37 +2511,37 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15-Apr-2022</t>
+          <t>10-Oct-2023</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Makeup Kit</t>
+          <t>T-shirt</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>100.6019586055559</v>
+        <v>330.4240915349662</v>
       </c>
       <c r="I54" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="55">
@@ -2528,15 +2550,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>07/28/2022</t>
+          <t>07/25/2023</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>145</v>
+        <v>265</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2544,18 +2566,20 @@
           <t>PayPal</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Returned</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Running Shoes</t>
+          <t>Jeans</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>1844.277071451179</v>
-      </c>
-      <c r="I55" t="n">
-        <v>4</v>
-      </c>
+        <v>1343.603345349049</v>
+      </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -2563,37 +2587,37 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>24-May-2023</t>
+          <t>01/11/2022</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>293</v>
+        <v>197</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>1345.725068085487</v>
+        <v>702.8597979521488</v>
       </c>
       <c r="I56" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57">
@@ -2602,11 +2626,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2022-01-31</t>
+          <t>2023-11-02</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>293</v>
+        <v>268</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2615,26 +2639,26 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Shoes</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1583.41 USD</t>
+          <t>789.90 USD</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58">
@@ -2643,39 +2667,39 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2022-01-26</t>
+          <t>03/31/2022</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>405</v>
+        <v>159</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Moisturizer</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>€1303,66</t>
+          <t>€556,99</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="59">
@@ -2684,37 +2708,37 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>02/27/2022</t>
+          <t>2022-07-02</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>267</v>
+        <v>295</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>796.9166447589693</v>
+        <v>859.7778642007689</v>
       </c>
       <c r="I59" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -2723,37 +2747,37 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>31-Jul-2023</t>
+          <t>30-Mar-2022</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>341</v>
+        <v>298</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Yoga Mat</t>
+          <t>T-shirt</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>347.4089175123578</v>
+        <v>545.4324816265162</v>
       </c>
       <c r="I60" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="61">
@@ -2762,37 +2786,37 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>06/23/2023</t>
+          <t>2023-01-28</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>199</v>
+        <v>440</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hairdryer</t>
+          <t>Yoga Mat</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>221.9451107986037</v>
+        <v>1698.566351333544</v>
       </c>
       <c r="I61" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -2801,15 +2825,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>07/25/2023</t>
+          <t>2022-08-19</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>208</v>
+        <v>325</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2819,21 +2843,21 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Toaster</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>$647.58</t>
+          <t>$357.34</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63">
@@ -2842,37 +2866,33 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2022-09-01</t>
+          <t>2023-09-14</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>495</v>
+        <v>257</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>PayPal</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>Returned</t>
-        </is>
-      </c>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Children's</t>
+          <t>Running Shoes</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>314.0856767403307</v>
+        <v>676.6085046646439</v>
       </c>
       <c r="I63" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -2881,37 +2901,37 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>05/05/2023</t>
+          <t>2023-02-01</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Moisturizer</t>
+          <t>Toaster</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>1956.322660416126</v>
+        <v>783.0268563969215</v>
       </c>
       <c r="I64" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -2920,11 +2940,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>28-Jan-2022</t>
+          <t>03-Aug-2023</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>453</v>
+        <v>347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2933,26 +2953,26 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Running Shoes</t>
+          <t>Tennis Racket</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>€1855,64</t>
+          <t>€273,03</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66">
@@ -2961,11 +2981,11 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>02/10/2023</t>
+          <t>05-Jan-2022</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>173</v>
+        <v>73</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2974,24 +2994,24 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Makeup Kit</t>
+          <t>Hairdryer</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>1180.899597802765</v>
+        <v>435.9880739886681</v>
       </c>
       <c r="I66" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="67">
@@ -3000,15 +3020,13 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>12/06/2023</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>93</v>
-      </c>
+          <t>09/19/2023</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -3023,16 +3041,16 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Dumbbells</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>1041.37 USD</t>
+          <t>116.93 USD</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="68">
@@ -3041,15 +3059,15 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2023-09-20</t>
+          <t>2023-09-25</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>139</v>
+        <v>456</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -3059,19 +3077,19 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Shoes</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>1444.450351145081</v>
+        <v>782.8047818154283</v>
       </c>
       <c r="I68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="69">
@@ -3080,37 +3098,37 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12/08/2022</t>
+          <t>2022-12-10</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>184</v>
+        <v>220</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dress</t>
+          <t>Vacuum Cleaner</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>416.5596098932847</v>
+        <v>112.4186341944711</v>
       </c>
       <c r="I69" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70">
@@ -3119,15 +3137,15 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2022-03-30</t>
+          <t>02/10/2023</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>98</v>
+        <v>359</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3137,20 +3155,18 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dress</t>
+          <t>Hairdryer</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>1979.108574357379</v>
-      </c>
-      <c r="I70" t="n">
-        <v>3</v>
-      </c>
+        <v>1587.081294591976</v>
+      </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -3158,20 +3174,20 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>18-Feb-2022</t>
+          <t>02/13/2022</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>363</v>
+        <v>211</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -3181,14 +3197,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Coffee Maker</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>1275.966353237679</v>
+        <v>656.5221498114264</v>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="72">
@@ -3197,39 +3213,39 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>31-Jan-2022</t>
+          <t>22-Apr-2023</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>20</v>
+        <v>114</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tennis Racket</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>$66.54</t>
+          <t>$1729.06</t>
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="73">
@@ -3238,35 +3254,37 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>12/24/2023</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
+          <t>28-Jun-2023</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>385</v>
+      </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Jacket</t>
+          <t>Fiction</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>737.5460912077722</v>
+        <v>670.5696880080437</v>
       </c>
       <c r="I73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -3275,11 +3293,11 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>10/27/2023</t>
+          <t>2022-04-09</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -3288,12 +3306,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -3302,10 +3320,10 @@
         </is>
       </c>
       <c r="H74" t="n">
-        <v>269.5293459955542</v>
+        <v>404.7327810770476</v>
       </c>
       <c r="I74" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="75">
@@ -3314,15 +3332,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>09/19/2023</t>
+          <t>09-Jun-2022</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>167</v>
+        <v>357</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3332,19 +3350,19 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>T-shirt</t>
+          <t>Toaster</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>11.82953066937164</v>
+        <v>1365.10627290055</v>
       </c>
       <c r="I75" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="76">
@@ -3353,30 +3371,34 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2022-12-20</t>
+          <t>14-Jul-2022</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>405</v>
+        <v>23</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Cash</t>
+        </is>
+      </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Blender</t>
+          <t>Toaster</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>459.9385350328267</v>
+        <v>1049.181990146988</v>
       </c>
       <c r="I76" t="n">
         <v>4</v>
@@ -3388,39 +3410,39 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2023-02-12</t>
+          <t>11/18/2023</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>500</v>
+        <v>15</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Running Shoes</t>
+          <t>Microwave</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>1864.67 USD</t>
+          <t>1780.70 USD</t>
         </is>
       </c>
       <c r="I77" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="78">
@@ -3429,15 +3451,15 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>10/09/2023</t>
+          <t>02/28/2022</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3447,19 +3469,19 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Blender</t>
+          <t>Jacket</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>159.9881979742034</v>
+        <v>1135.843098675749</v>
       </c>
       <c r="I78" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="79">
@@ -3468,35 +3490,35 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>11/08/2022</t>
+          <t>2023-07-28</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>375</v>
+        <v>297</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Credit Card</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr"/>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Fiction</t>
-        </is>
-      </c>
+          <t>PayPal</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Delivered</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>€1854,77</t>
+          <t>€1392,94</t>
         </is>
       </c>
       <c r="I79" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -3505,37 +3527,37 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>09-Mar-2022</t>
+          <t>2023-03-12</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>365</v>
+        <v>265</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dress</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>874.0585337151639</v>
+        <v>157.3045561138375</v>
       </c>
       <c r="I80" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81">
@@ -3544,37 +3566,37 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>01-Nov-2023</t>
+          <t>13-Oct-2022</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>46</v>
+        <v>291</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Jacket</t>
+          <t>Tablet</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>1621.069060011921</v>
+        <v>1839.105635125585</v>
       </c>
       <c r="I81" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="82">
@@ -3583,10 +3605,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>11-Oct-2023</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
+          <t>12-Jun-2023</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>371</v>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
           <t>Home &amp; Kitchen</t>
@@ -3599,21 +3623,21 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Toaster</t>
+          <t>Coffee Maker</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>$1473.53</t>
+          <t>$274.98</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="83">
@@ -3622,37 +3646,35 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>04-May-2023</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>450</v>
-      </c>
+          <t>06/15/2023</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Jacket</t>
+          <t>Coffee Maker</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>174.3174075197289</v>
+        <v>1519.121677177204</v>
       </c>
       <c r="I83" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="84">
@@ -3661,33 +3683,37 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2023-03-26</t>
+          <t>2023-06-19</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr"/>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Coffee Maker</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>1924.864035338578</v>
+        <v>1514.36006494231</v>
       </c>
       <c r="I84" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85">
@@ -3696,38 +3722,36 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>28-Oct-2022</t>
+          <t>12/20/2023</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>63</v>
+        <v>188</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Jacket</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>516.0729754432997</v>
-      </c>
-      <c r="I85" t="n">
-        <v>4</v>
-      </c>
+        <v>306.5660155387876</v>
+      </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -3735,15 +3759,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2023-03-14</t>
+          <t>2022-05-08</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>318</v>
+        <v>242</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3753,21 +3777,21 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>T-shirt</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>€636,40</t>
+          <t>€1878,24</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="87">
@@ -3776,15 +3800,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30-Mar-2022</t>
+          <t>06-Jun-2023</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>380</v>
+        <v>273</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3794,21 +3818,21 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Perfume</t>
+          <t>Running Shoes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>1362.11 USD</t>
+          <t>1547.91 USD</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="88">
@@ -3817,17 +3841,13 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2022-07-04</t>
+          <t>09-Dec-2023</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>209</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Beauty</t>
-        </is>
-      </c>
+        <v>55</v>
+      </c>
+      <c r="D88" t="inlineStr"/>
       <c r="E88" t="inlineStr">
         <is>
           <t>Cash</t>
@@ -3835,16 +3855,18 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr"/>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Running Shoes</t>
+        </is>
+      </c>
       <c r="H88" t="n">
-        <v>1561.273764541624</v>
-      </c>
-      <c r="I88" t="n">
-        <v>4</v>
-      </c>
+        <v>1107.481695903237</v>
+      </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -3852,34 +3874,34 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2022-03-21</t>
+          <t>27-Aug-2022</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>294</v>
+        <v>98</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Blender</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>1308.36602015888</v>
+        <v>719.4728544832531</v>
       </c>
       <c r="I89" t="n">
         <v>10</v>
@@ -3891,15 +3913,15 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>15-Oct-2022</t>
+          <t>2023-03-15</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>213</v>
+        <v>239</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3909,19 +3931,19 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Running Shoes</t>
+          <t>Laptop</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>414.9098982337766</v>
+        <v>690.1924779518572</v>
       </c>
       <c r="I90" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="91">
@@ -3930,37 +3952,37 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>08/18/2023</t>
+          <t>2023-03-25</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>134</v>
+        <v>175</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>1473.255354772404</v>
+        <v>453.4432706193373</v>
       </c>
       <c r="I91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="92">
@@ -3969,22 +3991,18 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2022-09-10</t>
+          <t>30-Aug-2023</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>136</v>
+        <v>223</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>Credit Card</t>
-        </is>
-      </c>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr"/>
       <c r="F92" t="inlineStr">
         <is>
           <t>Shipped</t>
@@ -3992,12 +4010,12 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Shoes</t>
+          <t>Non-fiction</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>$376.40</t>
+          <t>$19.75</t>
         </is>
       </c>
       <c r="I92" t="n">
@@ -4010,11 +4028,11 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2022-09-24</t>
+          <t>2023-09-12</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>4</v>
+        <v>379</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -4023,27 +4041,25 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Shampoo</t>
+          <t>Perfume</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>€686,79</t>
-        </is>
-      </c>
-      <c r="I93" t="n">
-        <v>3</v>
-      </c>
+          <t>€1704,53</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -4051,15 +4067,15 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>01/12/2023</t>
+          <t>08/24/2023</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>99</v>
+        <v>453</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4069,19 +4085,19 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Textbook</t>
+          <t>Coffee Maker</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>1319.786502550965</v>
+        <v>400.1981779184312</v>
       </c>
       <c r="I94" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95">
@@ -4090,37 +4106,37 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>21-Feb-2023</t>
+          <t>2023-06-09</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Yoga Mat</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>1273.518926301754</v>
+        <v>351.9572640852278</v>
       </c>
       <c r="I95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -4129,38 +4145,36 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2022-02-09</t>
+          <t>05/16/2023</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>63</v>
+        <v>378</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Dress</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>1878.27734539757</v>
-      </c>
-      <c r="I96" t="n">
-        <v>3</v>
-      </c>
+        <v>756.8108169509543</v>
+      </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -4168,39 +4182,39 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>08-Sep-2023</t>
+          <t>08/08/2022</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Tennis Racket</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>1061.72 USD</t>
+          <t>320.60 USD</t>
         </is>
       </c>
       <c r="I97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="98">
@@ -4209,37 +4223,37 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>30-Aug-2022</t>
+          <t>06/08/2022</t>
         </is>
       </c>
       <c r="C98" t="n">
+        <v>135</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>CANCELLED</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Jeans</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>511.6549368610742</v>
+      </c>
+      <c r="I98" t="n">
         <v>1</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Credit Card</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>Headphones</t>
-        </is>
-      </c>
-      <c r="H98" t="n">
-        <v>1098.056558594078</v>
-      </c>
-      <c r="I98" t="n">
-        <v>7</v>
       </c>
     </row>
     <row r="99">
@@ -4248,37 +4262,33 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2022-10-20</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>459</v>
+        <v>475</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Electronics</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>Credit Card</t>
-        </is>
-      </c>
+          <t>Books</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr"/>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Non-fiction</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>1913.319207415861</v>
+        <v>587.8979547334839</v>
       </c>
       <c r="I99" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="100">
@@ -4287,31 +4297,31 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>08-Feb-2023</t>
+          <t>10/26/2023</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>27</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>Clothing</t>
-        </is>
-      </c>
+        <v>431</v>
+      </c>
+      <c r="D100" t="inlineStr"/>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr"/>
+          <t>Cash</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>T-shirt</t>
+          <t>Yoga Mat</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>€1809,47</t>
+          <t>€1271,22</t>
         </is>
       </c>
       <c r="I100" t="n">
@@ -4324,37 +4334,33 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>02/13/2023</t>
+          <t>11/22/2023</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>20</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>Home &amp; Kitchen</t>
-        </is>
-      </c>
+        <v>269</v>
+      </c>
+      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Coffee Maker</t>
+          <t>Dress</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>245.3402968597829</v>
+        <v>742.2898518519489</v>
       </c>
       <c r="I101" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="102">
@@ -4363,38 +4369,40 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2022-04-16</t>
+          <t>12-Feb-2022</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>484</v>
+        <v>350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>T-shirt</t>
+          <t>Non-fiction</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>$1323.11</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>$1493.98</t>
+        </is>
+      </c>
+      <c r="I102" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -4402,38 +4410,36 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>06-Dec-2022</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>196</v>
+        <v>14</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Vacuum Cleaner</t>
+          <t>Jeans</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>526.1850136243021</v>
-      </c>
-      <c r="I103" t="n">
-        <v>8</v>
-      </c>
+        <v>1035.975667681632</v>
+      </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -4441,37 +4447,37 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2023-05-10</t>
+          <t>10/31/2023</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>453</v>
+        <v>125</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Children's</t>
+          <t>Vacuum Cleaner</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>291.6298909504314</v>
+        <v>1772.726300897877</v>
       </c>
       <c r="I104" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
@@ -4480,37 +4486,37 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2022-04-03</t>
+          <t>08/11/2022</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>147</v>
+        <v>402</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Shampoo</t>
+          <t>Dress</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>544.8105715053073</v>
+        <v>742.5711177672272</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="106">
@@ -4519,15 +4525,15 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2022-11-09</t>
+          <t>2022-11-27</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>227</v>
+        <v>304</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4537,19 +4543,15 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>Shampoo</t>
-        </is>
-      </c>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr"/>
       <c r="H106" t="n">
-        <v>1797.867931932708</v>
+        <v>1675.949185635379</v>
       </c>
       <c r="I106" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="107">
@@ -4558,39 +4560,35 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2023-04-19</t>
+          <t>13-Jul-2022</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>217</v>
+        <v>404</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Books</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>Bank Transfer</t>
-        </is>
-      </c>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr"/>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>€21,41</t>
+          <t>€917,35</t>
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
@@ -4599,37 +4597,37 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2023-03-08</t>
+          <t>01-Mar-2023</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>66</v>
+        <v>231</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Vacuum Cleaner</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>113.1899650355225</v>
+        <v>1283.530090617457</v>
       </c>
       <c r="I108" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="109">
@@ -4638,38 +4636,36 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>27-Apr-2023</t>
+          <t>2023-10-20</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>49</v>
+        <v>126</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Tennis Racket</t>
+          <t>Non-fiction</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>444.8296430178846</v>
-      </c>
-      <c r="I109" t="n">
-        <v>10</v>
-      </c>
+        <v>1502.018183091855</v>
+      </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -4677,37 +4673,35 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2022-03-20</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>188</v>
-      </c>
+          <t>04-Oct-2022</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Non-fiction</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>17.71006524651162</v>
+        <v>1600.042048419568</v>
       </c>
       <c r="I110" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="111">
@@ -4716,37 +4710,33 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2023-12-20</t>
+          <t>06/10/2022</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>421</v>
+        <v>484</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Returned</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>Makeup Kit</t>
-        </is>
-      </c>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr"/>
       <c r="H111" t="n">
-        <v>1126.971688263328</v>
+        <v>1431.228923488371</v>
       </c>
       <c r="I111" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="112">
@@ -4755,11 +4745,11 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>26-May-2023</t>
+          <t>17-Jan-2022</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -4773,21 +4763,21 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Tennis Racket</t>
+          <t>Dumbbells</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>$1751.64</t>
+          <t>$379.22</t>
         </is>
       </c>
       <c r="I112" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -4796,20 +4786,20 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20-Feb-2023</t>
+          <t>2022-09-11</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>5</v>
+        <v>158</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4819,14 +4809,14 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Smartphone</t>
+          <t>Jacket</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>1604.371151808053</v>
+        <v>104.0202557111256</v>
       </c>
       <c r="I113" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="114">
@@ -4835,15 +4825,15 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2023-01-29</t>
+          <t>22-Mar-2022</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4851,19 +4841,23 @@
           <t>Credit Card</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr"/>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Non-fiction</t>
+          <t>Hairdryer</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>€1555,72</t>
+          <t>€511,45</t>
         </is>
       </c>
       <c r="I114" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="115">
@@ -4872,37 +4866,33 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>07-Jan-2022</t>
+          <t>08/07/2023</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>351</v>
+        <v>453</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Clothing</t>
-        </is>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
+          <t>Home &amp; Kitchen</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr"/>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Jacket</t>
+          <t>Blender</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>1807.438570894656</v>
+        <v>158.210095648613</v>
       </c>
       <c r="I115" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
     </row>
     <row r="116">
@@ -4911,33 +4901,37 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>06-Oct-2022</t>
+          <t>01-Jul-2022</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>349</v>
-      </c>
-      <c r="D116" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Home &amp; Kitchen</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Basketball</t>
+          <t>Coffee Maker</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>205.9085554332241</v>
+        <v>1703.341700334928</v>
       </c>
       <c r="I116" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
@@ -4946,39 +4940,39 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>08-Apr-2023</t>
+          <t>2022-08-18</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>340</v>
+        <v>40</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Textbook</t>
+          <t>Running Shoes</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>784.10 USD</t>
+          <t>644.00 USD</t>
         </is>
       </c>
       <c r="I117" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="118">
@@ -4987,15 +4981,15 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>01-May-2023</t>
+          <t>30-Nov-2022</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>499</v>
+        <v>88</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5010,14 +5004,14 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>663.4864360146903</v>
+        <v>321.97073146181</v>
       </c>
       <c r="I118" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119">
@@ -5026,11 +5020,11 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2023-11-28</t>
+          <t>02/06/2022</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>50</v>
+        <v>459</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -5039,12 +5033,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -5053,10 +5047,10 @@
         </is>
       </c>
       <c r="H119" t="n">
-        <v>847.8828959362679</v>
+        <v>1870.477892384396</v>
       </c>
       <c r="I119" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
     </row>
     <row r="120">
@@ -5065,37 +5059,33 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>05-Feb-2023</t>
+          <t>2023-06-24</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>64</v>
+        <v>224</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Beauty</t>
-        </is>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>Check</t>
-        </is>
-      </c>
+          <t>Clothing</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr"/>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Perfume</t>
+          <t>Shoes</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>1995.26022221558</v>
+        <v>804.1099680236573</v>
       </c>
       <c r="I120" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="121">
@@ -5104,15 +5094,15 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>08/10/2022</t>
+          <t>2022-06-17</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>289</v>
+        <v>357</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -5120,23 +5110,19 @@
           <t>Credit Card</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
+      <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Tennis Racket</t>
+          <t>Vacuum Cleaner</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>€1669,90</t>
+          <t>€1779,22</t>
         </is>
       </c>
       <c r="I121" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="122">
@@ -5145,40 +5131,30 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>06/13/2023</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>250</v>
+        <v>8</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Headphones</t>
-        </is>
-      </c>
+          <t>Check</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>$857.40</t>
-        </is>
-      </c>
-      <c r="I122" t="n">
-        <v>9</v>
-      </c>
+          <t>$1456.09</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -5186,15 +5162,15 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>2023-03-01</t>
+          <t>11-Aug-2022</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>24</v>
+        <v>243</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5204,19 +5180,19 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Shoes</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>337.4672867169492</v>
+        <v>1190.958874057737</v>
       </c>
       <c r="I123" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="124">
@@ -5225,12 +5201,10 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>25-Jan-2022</t>
-        </is>
-      </c>
-      <c r="C124" t="n">
-        <v>150</v>
-      </c>
+          <t>05/15/2022</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr"/>
       <c r="D124" t="inlineStr">
         <is>
           <t>Beauty</t>
@@ -5238,24 +5212,24 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Makeup Kit</t>
+          <t>Hairdryer</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>600.5188614711076</v>
+        <v>1707.374951435246</v>
       </c>
       <c r="I124" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125">
@@ -5264,15 +5238,15 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>02-Nov-2023</t>
+          <t>2023-04-23</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>293</v>
+        <v>57</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5282,19 +5256,19 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Toaster</t>
+          <t>Yoga Mat</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>146.3038880877378</v>
+        <v>843.6050362849788</v>
       </c>
       <c r="I125" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="126">
@@ -5303,38 +5277,36 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>2022-12-19</t>
+          <t>08-Oct-2023</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>416</v>
+        <v>140</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Headphones</t>
+          <t>T-shirt</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>1436.637656887094</v>
-      </c>
-      <c r="I126" t="n">
-        <v>1</v>
-      </c>
+        <v>1860.718884652432</v>
+      </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -5342,35 +5314,35 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>22-Dec-2022</t>
+          <t>2022-07-06</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>353</v>
+        <v>110</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Pending</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1662.67 USD</t>
+          <t>1569.63 USD</t>
         </is>
       </c>
       <c r="I127" t="n">
@@ -5383,11 +5355,11 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>06/27/2023</t>
+          <t>20-Nov-2023</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>352</v>
+        <v>384</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -5396,26 +5368,26 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Smartphone</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>€1277,11</t>
+          <t>€822,85</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="129">
@@ -5424,15 +5396,15 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>12/23/2023</t>
+          <t>09/21/2023</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>410</v>
+        <v>154</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Beauty</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5442,19 +5414,19 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Biography</t>
+          <t>Hairdryer</t>
         </is>
       </c>
       <c r="H129" t="n">
-        <v>1670.86705796247</v>
+        <v>1825.536299341313</v>
       </c>
       <c r="I129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="130">
@@ -5463,37 +5435,37 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>2022-09-17</t>
+          <t>20-Sep-2023</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>156</v>
+        <v>446</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Tennis Racket</t>
+          <t>Biography</t>
         </is>
       </c>
       <c r="H130" t="n">
-        <v>1694.958913446467</v>
+        <v>837.8328015669814</v>
       </c>
       <c r="I130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="131">
@@ -5502,11 +5474,11 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>2023-05-06</t>
+          <t>02-Mar-2023</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>171</v>
+        <v>328</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -5515,7 +5487,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5529,9 +5501,11 @@
         </is>
       </c>
       <c r="H131" t="n">
-        <v>1964.837712734124</v>
-      </c>
-      <c r="I131" t="inlineStr"/>
+        <v>1000.606626001028</v>
+      </c>
+      <c r="I131" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -5539,39 +5513,39 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
+          <t>27-Feb-2022</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>386</v>
+        <v>149</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Children's</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>$988.52</t>
+          <t>$313.69</t>
         </is>
       </c>
       <c r="I132" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="133">
@@ -5580,15 +5554,15 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>01-Apr-2022</t>
+          <t>2023-11-20</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>128</v>
+        <v>420</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5598,19 +5572,19 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Laptop</t>
+          <t>Jacket</t>
         </is>
       </c>
       <c r="H133" t="n">
-        <v>1536.996763337478</v>
+        <v>561.4876125873194</v>
       </c>
       <c r="I133" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="134">
@@ -5619,37 +5593,37 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>2023-08-14</t>
+          <t>2022-10-08</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>156</v>
+        <v>426</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Basketball</t>
         </is>
       </c>
       <c r="H134" t="n">
-        <v>324.1222164127788</v>
+        <v>309.8044298490724</v>
       </c>
       <c r="I134" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="135">
@@ -5658,35 +5632,39 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>06-Sep-2023</t>
+          <t>31-Aug-2023</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>98</v>
+        <v>41</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Check</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr"/>
+          <t>Bank Transfer</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Shipped</t>
+        </is>
+      </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Headphones</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>€1162,40</t>
+          <t>€1339,43</t>
         </is>
       </c>
       <c r="I135" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="136">
@@ -5695,36 +5673,38 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>17-Jun-2023</t>
+          <t>01/26/2023</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Sports</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Shipped</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Running Shoes</t>
+          <t>Microwave</t>
         </is>
       </c>
       <c r="H136" t="n">
-        <v>1824.970970417849</v>
-      </c>
-      <c r="I136" t="inlineStr"/>
+        <v>828.594349473471</v>
+      </c>
+      <c r="I136" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -5732,35 +5712,35 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>23-Dec-2023</t>
+          <t>2022-09-17</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>171</v>
+        <v>354</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Books</t>
+          <t>Sports</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Credit Card</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fiction</t>
+          <t>Dumbbells</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>134.98 USD</t>
+          <t>1934.73 USD</t>
         </is>
       </c>
       <c r="I137" t="n">
@@ -5773,29 +5753,37 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>02/12/2022</t>
+          <t>04-Jun-2022</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>107</v>
+        <v>13</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Beauty</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr"/>
+          <t>Sports</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>PayPal</t>
+        </is>
+      </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr"/>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Running Shoes</t>
+        </is>
+      </c>
       <c r="H138" t="n">
-        <v>1737.408383172806</v>
+        <v>1436.117308537984</v>
       </c>
       <c r="I138" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="139">
@@ -5804,15 +5792,15 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>2022-09-15</t>
+          <t>18-May-2023</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>486</v>
+        <v>258</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5822,19 +5810,15 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>Jacket</t>
-        </is>
-      </c>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr"/>
       <c r="H139" t="n">
-        <v>738.5692765616187</v>
+        <v>1194.74209981064</v>
       </c>
       <c r="I139" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="140">
@@ -5843,33 +5827,37 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>03-Dec-2022</t>
+          <t>23-May-2022</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>397</v>
+        <v>143</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Beauty</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>PayPal</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr"/>
+          <t>Returned</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Laptop</t>
+        </is>
+      </c>
       <c r="H140" t="n">
-        <v>298.4478376502215</v>
+        <v>1958.491264457406</v>
       </c>
       <c r="I140" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141">
@@ -5878,15 +5866,15 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>04/11/2022</t>
+          <t>29-Nov-2022</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>358</v>
+        <v>122</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Home &amp; Kitchen</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5896,19 +5884,19 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Camera</t>
+          <t>Coffee Maker</t>
         </is>
       </c>
       <c r="H141" t="n">
-        <v>1421.054374147787</v>
+        <v>644.9672083947789</v>
       </c>
       <c r="I141" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="142">
@@ -5917,10 +5905,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>2022-07-01</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr"/>
+          <t>04/27/2023</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>133</v>
+      </c>
       <c r="D142" t="inlineStr">
         <is>
           <t>Sports</t>
@@ -5938,16 +5928,16 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Dumbbells</t>
+          <t>Yoga Mat</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>$1180.21</t>
+          <t>$1297.81</t>
         </is>
       </c>
       <c r="I142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="143">
@@ -5956,37 +5946,37 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>03-Jul-2022</t>
+          <t>2023-12-29</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>456</v>
+        <v>144</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Books</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Dress</t>
+          <t>Non-fiction</t>
         </is>
       </c>
       <c r="H143" t="n">
-        <v>784.1626197636283</v>
+        <v>1730.544956598728</v>
       </c>
       <c r="I143" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="144">
@@ -5995,37 +5985,37 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>03-Jul-2022</t>
+          <t>11-Jan-2022</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>292</v>
+        <v>231</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Clothing</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>Returned</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Jeans</t>
+          <t>Camera</t>
         </is>
       </c>
       <c r="H144" t="n">
-        <v>1138.686239340383</v>
+        <v>1660.462271843616</v>
       </c>
       <c r="I144" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="145">
@@ -6034,11 +6024,11 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>2022-02-11</t>
+          <t>03-Nov-2022</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>178</v>
+        <v>482</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -6047,24 +6037,24 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Check</t>
+          <t>Cash</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Vacuum Cleaner</t>
+          <t>Microwave</t>
         </is>
       </c>
       <c r="H145" t="n">
-        <v>1552.318864273661</v>
+        <v>1476.358184678883</v>
       </c>
       <c r="I145" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="146">
@@ -6073,11 +6063,11 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>2022-06-12</t>
+          <t>09/20/2022</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>33</v>
+        <v>268</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -6086,24 +6076,24 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Delivered</t>
+          <t>CANCELLED</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Yoga Mat</t>
+          <t>Tennis Racket</t>
         </is>
       </c>
       <c r="H146" t="n">
-        <v>1216.403351812916</v>
+        <v>239.1770207639263</v>
       </c>
       <c r="I146" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="147">
@@ -6112,35 +6102,37 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>2022-12-05</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>144</v>
-      </c>
-      <c r="D147" t="inlineStr"/>
+          <t>2022-09-30</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Sports</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Bank Transfer</t>
+          <t>Credit Card</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Returned</t>
+          <t>Delivered</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hairdryer</t>
+          <t>Tennis Racket</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>1652.31 USD</t>
+          <t>783.97 USD</t>
         </is>
       </c>
       <c r="I147" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="148">
@@ -6149,11 +6141,11 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>06/06/2022</t>
+          <t>2022-09-12</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>33</v>
+        <v>216</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -6162,20 +6154,24 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Check</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Shipped</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr"/>
+          <t>Pending</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Moisturizer</t>
+        </is>
+      </c>
       <c r="H148" t="n">
-        <v>1429.830000575741</v>
+        <v>109.7064389429519</v>
       </c>
       <c r="I148" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="149">
@@ -6184,11 +6180,11 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>2023-03-09</t>
+          <t>03-Jun-2022</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>319</v>
+        <v>23</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -6197,26 +6193,26 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>PayPal</t>
+          <t>Bank Transfer</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>CANCELLED</t>
+          <t>Shipped</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Moisturizer</t>
+          <t>Perfume</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>€157,86</t>
+          <t>€1995,95</t>
         </is>
       </c>
       <c r="I149" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="150">
@@ -6225,11 +6221,11 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>2023-12-15</t>
+          <t>20-May-2022</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>21</v>
+        <v>198</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -6243,19 +6239,15 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Delivered</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>Fiction</t>
-        </is>
-      </c>
+          <t>Shipped</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr"/>
       <c r="H150" t="n">
-        <v>1506.542340990286</v>
+        <v>192.6852734258331</v>
       </c>
       <c r="I150" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="151">
@@ -6264,13 +6256,15 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>13-Jul-2022</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr"/>
+          <t>2023-12-11</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>72</v>
+      </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Clothing</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6285,14 +6279,14 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>T-shirt</t>
         </is>
       </c>
       <c r="H151" t="n">
-        <v>534.9345553257575</v>
+        <v>1148.177351159166</v>
       </c>
       <c r="I151" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
